--- a/tables/Table 2 Model selection.xlsx
+++ b/tables/Table 2 Model selection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\OSM_red_squirrel_distribution\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C253D74-AEAA-486B-83D9-5DE6A9DD182F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B25844C-459B-4BEF-82C4-E541C97AB69B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,9 +40,6 @@
     <t>AICw</t>
   </si>
   <si>
-    <t>CORE + Edge Density + Cumulative Disturbance</t>
-  </si>
-  <si>
     <t>CORE + Pipelines &amp; Transmission Lines + Seismic Lines + Inactive Well Sites + Harvest &lt;15</t>
   </si>
   <si>
@@ -119,9 +116,6 @@
   </si>
   <si>
     <t>Configuration</t>
-  </si>
-  <si>
-    <t>CORE + Edge Density × Cumulative Disturbance</t>
   </si>
   <si>
     <r>
@@ -146,6 +140,12 @@
       </rPr>
       <t xml:space="preserve"> composition</t>
     </r>
+  </si>
+  <si>
+    <t>CORE + Edge Density × Cumulative Footprint</t>
+  </si>
+  <si>
+    <t>CORE + Edge Density + Cumulative Footprint</t>
   </si>
 </sst>
 </file>
@@ -244,7 +244,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -317,7 +317,6 @@
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -635,17 +634,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
-    <col min="2" max="2" width="21.42578125" customWidth="1"/>
-    <col min="3" max="3" width="61.5703125" customWidth="1"/>
-    <col min="4" max="4" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" customWidth="1"/>
+    <col min="3" max="3" width="61.5546875" customWidth="1"/>
+    <col min="4" max="4" width="3.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -658,7 +657,7 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="8" t="s">
         <v>0</v>
@@ -683,10 +682,10 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>33</v>
@@ -708,13 +707,13 @@
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
     </row>
-    <row r="4" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="B4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>6</v>
       </c>
       <c r="D4" s="13">
         <v>9</v>
@@ -733,13 +732,13 @@
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
     </row>
-    <row r="5" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" s="13">
         <v>11</v>
@@ -758,13 +757,13 @@
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
     </row>
-    <row r="6" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" s="13">
         <v>10</v>
@@ -783,13 +782,13 @@
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
     </row>
-    <row r="7" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="13">
         <v>9</v>
@@ -808,13 +807,13 @@
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
     </row>
-    <row r="8" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
       <c r="B8" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="13">
         <v>13</v>
@@ -833,13 +832,13 @@
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
     </row>
-    <row r="9" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
       <c r="B9" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" s="13">
         <v>12</v>
@@ -858,13 +857,13 @@
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
       <c r="B10" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D10" s="13">
         <v>8</v>
@@ -883,13 +882,13 @@
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
     </row>
-    <row r="11" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="B11" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D11" s="13">
         <v>10</v>
@@ -908,13 +907,13 @@
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
     </row>
-    <row r="12" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
       <c r="B12" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D12" s="13">
         <v>9</v>
@@ -933,13 +932,13 @@
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
     </row>
-    <row r="13" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
       <c r="B13" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D13" s="13">
         <v>8</v>
@@ -958,13 +957,13 @@
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
     </row>
-    <row r="14" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="B14" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D14" s="13">
         <v>9</v>
@@ -983,13 +982,13 @@
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
     </row>
-    <row r="15" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D15" s="13">
         <v>8</v>
@@ -1008,24 +1007,24 @@
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
     </row>
-    <row r="16" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="B16" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="28">
+        <v>30</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="27">
         <v>7</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="28">
         <v>1840.3967542116741</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="28">
         <v>12.341330508078951</v>
       </c>
-      <c r="G16" s="30">
+      <c r="G16" s="29">
         <v>1.8071709624814429E-3</v>
       </c>
       <c r="H16" s="5"/>
@@ -1033,13 +1032,13 @@
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
     </row>
-    <row r="17" spans="1:11" s="26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D17" s="23">
         <v>10</v>
@@ -1058,13 +1057,13 @@
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
     </row>
-    <row r="18" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D18" s="13">
         <v>8</v>
@@ -1083,13 +1082,13 @@
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
     </row>
-    <row r="19" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
       <c r="B19" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D19" s="13">
         <v>9</v>
@@ -1108,13 +1107,13 @@
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
     </row>
-    <row r="20" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
       <c r="B20" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D20" s="13">
         <v>8</v>
@@ -1133,13 +1132,13 @@
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
     </row>
-    <row r="21" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
       <c r="B21" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D21" s="13">
         <v>9</v>
@@ -1158,13 +1157,13 @@
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
     </row>
-    <row r="22" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
       <c r="B22" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D22" s="13">
         <v>9</v>
@@ -1183,13 +1182,13 @@
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
     </row>
-    <row r="23" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
       <c r="B23" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D23" s="13">
         <v>6</v>
@@ -1208,13 +1207,13 @@
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
     </row>
-    <row r="24" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
       <c r="B24" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D24" s="13">
         <v>4</v>
@@ -1233,10 +1232,10 @@
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
     </row>
-    <row r="25" spans="1:11" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5"/>
       <c r="B25" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C25" s="16">
         <v>1</v>
@@ -1258,7 +1257,7 @@
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -1271,7 +1270,7 @@
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -1284,7 +1283,7 @@
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -1297,7 +1296,7 @@
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -1310,7 +1309,7 @@
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
